--- a/artfynd/A 3777-2026 artfynd.xlsx
+++ b/artfynd/A 3777-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92881205</v>
+        <v>92881218</v>
       </c>
       <c r="B3" t="n">
-        <v>98693</v>
+        <v>97524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,23 +797,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>221944</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -875,7 +871,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 170008L</t>
+          <t>Gst Fyndnr 169995L</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>92881234</v>
+        <v>92881205</v>
       </c>
       <c r="B4" t="n">
-        <v>100847</v>
+        <v>98693</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -986,7 +982,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 169983L</t>
+          <t>Gst Fyndnr 170008L</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>92881220</v>
+        <v>92881234</v>
       </c>
       <c r="B5" t="n">
-        <v>97530</v>
+        <v>100847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1097,7 +1093,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 169994L</t>
+          <t>Gst Fyndnr 169983L</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1119,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>92881251</v>
+        <v>92881220</v>
       </c>
       <c r="B6" t="n">
-        <v>98558</v>
+        <v>97530</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219795</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1208,7 +1204,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 169966L</t>
+          <t>Gst Fyndnr 169994L</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1223,6 +1219,117 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>92881251</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98558</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>ÅMOT, KÄLLÄNGET, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>579920</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6760090</v>
+      </c>
+      <c r="S7" t="n">
+        <v>100</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1998-06-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1998-06-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Blandade biotoper/SKOG MED KÄLLA/ UTBYGGD TILL VATTENTÄKT/ RESTER AV ODLINGMARK/ VÄGKANTER.</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 169966L</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Delin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Gästriklands flora (2016)</t>
         </is>
